--- a/TBRM Machining BV/Production Orders_2026-04-28.xlsx
+++ b/TBRM Machining BV/Production Orders_2026-04-28.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\d.vandriel\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MFI\Documents\GitHub\ProductionPlanning\TBRM Machining BV\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B5A4034B-C355-4766-BD25-06002AA8ED23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{790EF431-95E4-4A61-BFB0-2F9B74D1BB40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -3683,12 +3683,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AC607"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="29" width="30.7109375" customWidth="1"/>
+    <col min="1" max="29" width="30.73046875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3777,7 +3777,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>29</v>
       </c>
@@ -3862,7 +3862,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="3" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -3911,7 +3911,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="4" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -3960,7 +3960,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="5" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -4009,7 +4009,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="6" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -4058,7 +4058,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="7" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
         <v>29</v>
       </c>
@@ -4143,7 +4143,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="8" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -4192,7 +4192,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="9" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -4241,7 +4241,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="10" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -4290,7 +4290,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="11" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A11" s="2" t="s">
         <v>29</v>
       </c>
@@ -4379,7 +4379,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="12" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -4428,7 +4428,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="13" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -4473,7 +4473,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="14" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -4518,7 +4518,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="15" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A15" s="2" t="s">
         <v>29</v>
       </c>
@@ -4607,7 +4607,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="16" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -4656,7 +4656,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="17" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
@@ -4705,7 +4705,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="18" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
@@ -4750,7 +4750,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="19" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -4795,7 +4795,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="20" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A20" s="2" t="s">
         <v>29</v>
       </c>
@@ -4884,7 +4884,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="21" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -4933,7 +4933,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="22" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -4978,7 +4978,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="23" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -5023,7 +5023,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="24" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A24" s="2" t="s">
         <v>29</v>
       </c>
@@ -5112,7 +5112,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="25" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -5161,7 +5161,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="26" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -5206,7 +5206,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="27" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -5251,7 +5251,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="28" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A28" s="2" t="s">
         <v>29</v>
       </c>
@@ -5340,7 +5340,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="29" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
@@ -5389,7 +5389,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="30" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -5438,7 +5438,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="31" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
@@ -5483,7 +5483,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="32" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
@@ -5528,7 +5528,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="33" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A33" s="2" t="s">
         <v>29</v>
       </c>
@@ -5617,7 +5617,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="34" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
@@ -5666,7 +5666,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="35" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
@@ -5715,7 +5715,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="36" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
@@ -5760,7 +5760,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="37" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A37" s="2" t="s">
         <v>29</v>
       </c>
@@ -5849,7 +5849,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="38" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
@@ -5898,7 +5898,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="39" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
@@ -5947,7 +5947,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="40" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
@@ -5996,7 +5996,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="41" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A41" s="2"/>
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
@@ -6045,7 +6045,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="42" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
@@ -6094,7 +6094,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="43" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
@@ -6143,7 +6143,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="44" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A44" s="2" t="s">
         <v>29</v>
       </c>
@@ -6232,7 +6232,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="45" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
@@ -6277,7 +6277,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="46" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
@@ -6322,7 +6322,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="47" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
@@ -6367,7 +6367,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="48" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
@@ -6412,7 +6412,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="49" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A49" s="2"/>
       <c r="B49" s="2"/>
       <c r="C49" s="2"/>
@@ -6457,7 +6457,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="50" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A50" s="2" t="s">
         <v>29</v>
       </c>
@@ -6542,7 +6542,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="51" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A51" s="2"/>
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
@@ -6587,7 +6587,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="52" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A52" s="2" t="s">
         <v>29</v>
       </c>
@@ -6672,7 +6672,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="53" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A53" s="2"/>
       <c r="B53" s="2"/>
       <c r="C53" s="2"/>
@@ -6717,7 +6717,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="54" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A54" s="2" t="s">
         <v>29</v>
       </c>
@@ -6806,7 +6806,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="55" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A55" s="2"/>
       <c r="B55" s="2"/>
       <c r="C55" s="2"/>
@@ -6855,7 +6855,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="56" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A56" s="2"/>
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
@@ -6904,7 +6904,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="57" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A57" s="2"/>
       <c r="B57" s="2"/>
       <c r="C57" s="2"/>
@@ -6953,7 +6953,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="58" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A58" s="2"/>
       <c r="B58" s="2"/>
       <c r="C58" s="2"/>
@@ -6998,7 +6998,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="59" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A59" s="2"/>
       <c r="B59" s="2"/>
       <c r="C59" s="2"/>
@@ -7043,7 +7043,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="60" spans="1:29" ht="45" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:29" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A60" s="2" t="s">
         <v>29</v>
       </c>
@@ -7128,7 +7128,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="61" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A61" s="2"/>
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
@@ -7173,7 +7173,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="62" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A62" s="2"/>
       <c r="B62" s="2"/>
       <c r="C62" s="2"/>
@@ -7218,7 +7218,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="63" spans="1:29" ht="60" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:29" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A63" s="2" t="s">
         <v>29</v>
       </c>
@@ -7289,7 +7289,7 @@
       <c r="AB63" s="2"/>
       <c r="AC63" s="2"/>
     </row>
-    <row r="64" spans="1:29" ht="60" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:29" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A64" s="2" t="s">
         <v>29</v>
       </c>
@@ -7360,7 +7360,7 @@
       <c r="AB64" s="2"/>
       <c r="AC64" s="2"/>
     </row>
-    <row r="65" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A65" s="2"/>
       <c r="B65" s="2"/>
       <c r="C65" s="2"/>
@@ -7397,7 +7397,7 @@
       <c r="AB65" s="2"/>
       <c r="AC65" s="2"/>
     </row>
-    <row r="66" spans="1:29" ht="60" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:29" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A66" s="2" t="s">
         <v>29</v>
       </c>
@@ -7468,7 +7468,7 @@
       <c r="AB66" s="2"/>
       <c r="AC66" s="2"/>
     </row>
-    <row r="67" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A67" s="2"/>
       <c r="B67" s="2"/>
       <c r="C67" s="2"/>
@@ -7505,7 +7505,7 @@
       <c r="AB67" s="2"/>
       <c r="AC67" s="2"/>
     </row>
-    <row r="68" spans="1:29" ht="60" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:29" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A68" s="2" t="s">
         <v>29</v>
       </c>
@@ -7576,7 +7576,7 @@
       <c r="AB68" s="2"/>
       <c r="AC68" s="2"/>
     </row>
-    <row r="69" spans="1:29" ht="45" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:29" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A69" s="2" t="s">
         <v>29</v>
       </c>
@@ -7665,7 +7665,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="70" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A70" s="2"/>
       <c r="B70" s="2"/>
       <c r="C70" s="2"/>
@@ -7714,7 +7714,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="71" spans="1:29" ht="45" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A71" s="2"/>
       <c r="B71" s="2"/>
       <c r="C71" s="2"/>
@@ -7759,7 +7759,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="72" spans="1:29" ht="45" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A72" s="2" t="s">
         <v>29</v>
       </c>
@@ -7848,7 +7848,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="73" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A73" s="2"/>
       <c r="B73" s="2"/>
       <c r="C73" s="2"/>
@@ -7893,7 +7893,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="74" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A74" s="2"/>
       <c r="B74" s="2"/>
       <c r="C74" s="2"/>
@@ -7938,7 +7938,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="75" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A75" s="2" t="s">
         <v>29</v>
       </c>
@@ -8027,7 +8027,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="76" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A76" s="2"/>
       <c r="B76" s="2"/>
       <c r="C76" s="2"/>
@@ -8072,7 +8072,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="77" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A77" s="2" t="s">
         <v>29</v>
       </c>
@@ -8161,7 +8161,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="78" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A78" s="2"/>
       <c r="B78" s="2"/>
       <c r="C78" s="2"/>
@@ -8210,7 +8210,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="79" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A79" s="2"/>
       <c r="B79" s="2"/>
       <c r="C79" s="2"/>
@@ -8259,7 +8259,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="80" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A80" s="2"/>
       <c r="B80" s="2"/>
       <c r="C80" s="2"/>
@@ -8304,7 +8304,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="81" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A81" s="2" t="s">
         <v>29</v>
       </c>
@@ -8393,7 +8393,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="82" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A82" s="2"/>
       <c r="B82" s="2"/>
       <c r="C82" s="2"/>
@@ -8438,7 +8438,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="83" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A83" s="2" t="s">
         <v>29</v>
       </c>
@@ -8527,7 +8527,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="84" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A84" s="2"/>
       <c r="B84" s="2"/>
       <c r="C84" s="2"/>
@@ -8572,7 +8572,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="85" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A85" s="2" t="s">
         <v>29</v>
       </c>
@@ -8661,7 +8661,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="86" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A86" s="2"/>
       <c r="B86" s="2"/>
       <c r="C86" s="2"/>
@@ -8706,7 +8706,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="87" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A87" s="2" t="s">
         <v>29</v>
       </c>
@@ -8795,7 +8795,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="88" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A88" s="2"/>
       <c r="B88" s="2"/>
       <c r="C88" s="2"/>
@@ -8844,7 +8844,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="89" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A89" s="2"/>
       <c r="B89" s="2"/>
       <c r="C89" s="2"/>
@@ -8893,7 +8893,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="90" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A90" s="2"/>
       <c r="B90" s="2"/>
       <c r="C90" s="2"/>
@@ -8938,7 +8938,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="91" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A91" s="2"/>
       <c r="B91" s="2"/>
       <c r="C91" s="2"/>
@@ -8983,7 +8983,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="92" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A92" s="2" t="s">
         <v>29</v>
       </c>
@@ -9072,7 +9072,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="93" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A93" s="2"/>
       <c r="B93" s="2"/>
       <c r="C93" s="2"/>
@@ -9117,7 +9117,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="94" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A94" s="2"/>
       <c r="B94" s="2"/>
       <c r="C94" s="2"/>
@@ -9162,7 +9162,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="95" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A95" s="2"/>
       <c r="B95" s="2"/>
       <c r="C95" s="2"/>
@@ -9207,7 +9207,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="96" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A96" s="2" t="s">
         <v>29</v>
       </c>
@@ -9296,7 +9296,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="97" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A97" s="2"/>
       <c r="B97" s="2"/>
       <c r="C97" s="2"/>
@@ -9341,7 +9341,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="98" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A98" s="2"/>
       <c r="B98" s="2"/>
       <c r="C98" s="2"/>
@@ -9386,7 +9386,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="99" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A99" s="2"/>
       <c r="B99" s="2"/>
       <c r="C99" s="2"/>
@@ -9431,7 +9431,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="100" spans="1:29" ht="45" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A100" s="2" t="s">
         <v>29</v>
       </c>
@@ -9520,7 +9520,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="101" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A101" s="2"/>
       <c r="B101" s="2"/>
       <c r="C101" s="2"/>
@@ -9565,7 +9565,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="102" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A102" s="2"/>
       <c r="B102" s="2"/>
       <c r="C102" s="2"/>
@@ -9610,7 +9610,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="103" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A103" s="2" t="s">
         <v>29</v>
       </c>
@@ -9699,7 +9699,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="104" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A104" s="2"/>
       <c r="B104" s="2"/>
       <c r="C104" s="2"/>
@@ -9744,7 +9744,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="105" spans="1:29" ht="45" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A105" s="2" t="s">
         <v>29</v>
       </c>
@@ -9833,7 +9833,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="106" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A106" s="2"/>
       <c r="B106" s="2"/>
       <c r="C106" s="2"/>
@@ -9878,7 +9878,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="107" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A107" s="2"/>
       <c r="B107" s="2"/>
       <c r="C107" s="2"/>
@@ -9927,7 +9927,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="108" spans="1:29" ht="45" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A108" s="2" t="s">
         <v>29</v>
       </c>
@@ -10016,7 +10016,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="109" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A109" s="2"/>
       <c r="B109" s="2"/>
       <c r="C109" s="2"/>
@@ -10061,7 +10061,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="110" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A110" s="2"/>
       <c r="B110" s="2"/>
       <c r="C110" s="2"/>
@@ -10106,7 +10106,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="111" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A111" s="2" t="s">
         <v>29</v>
       </c>
@@ -10195,7 +10195,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="112" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A112" s="2"/>
       <c r="B112" s="2"/>
       <c r="C112" s="2"/>
@@ -10240,7 +10240,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="113" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A113" s="2"/>
       <c r="B113" s="2"/>
       <c r="C113" s="2"/>
@@ -10285,7 +10285,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="114" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A114" s="2"/>
       <c r="B114" s="2"/>
       <c r="C114" s="2"/>
@@ -10330,7 +10330,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="115" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A115" s="2" t="s">
         <v>29</v>
       </c>
@@ -10419,7 +10419,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="116" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A116" s="2"/>
       <c r="B116" s="2"/>
       <c r="C116" s="2"/>
@@ -10464,7 +10464,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="117" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A117" s="2"/>
       <c r="B117" s="2"/>
       <c r="C117" s="2"/>
@@ -10509,7 +10509,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="118" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A118" s="2"/>
       <c r="B118" s="2"/>
       <c r="C118" s="2"/>
@@ -10554,7 +10554,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="119" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A119" s="2"/>
       <c r="B119" s="2"/>
       <c r="C119" s="2"/>
@@ -10599,7 +10599,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="120" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A120" s="2"/>
       <c r="B120" s="2"/>
       <c r="C120" s="2"/>
@@ -10644,7 +10644,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="121" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A121" s="2" t="s">
         <v>29</v>
       </c>
@@ -10733,7 +10733,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="122" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A122" s="2"/>
       <c r="B122" s="2"/>
       <c r="C122" s="2"/>
@@ -10778,7 +10778,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="123" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A123" s="2"/>
       <c r="B123" s="2"/>
       <c r="C123" s="2"/>
@@ -10823,7 +10823,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="124" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A124" s="2" t="s">
         <v>29</v>
       </c>
@@ -10912,7 +10912,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="125" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A125" s="2"/>
       <c r="B125" s="2"/>
       <c r="C125" s="2"/>
@@ -10957,7 +10957,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="126" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A126" s="2"/>
       <c r="B126" s="2"/>
       <c r="C126" s="2"/>
@@ -11002,7 +11002,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="127" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A127" s="2" t="s">
         <v>29</v>
       </c>
@@ -11081,7 +11081,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="128" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A128" s="2"/>
       <c r="B128" s="2"/>
       <c r="C128" s="2"/>
@@ -11126,7 +11126,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="129" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A129" s="2"/>
       <c r="B129" s="2"/>
       <c r="C129" s="2"/>
@@ -11171,7 +11171,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="130" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A130" s="2" t="s">
         <v>29</v>
       </c>
@@ -11260,7 +11260,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="131" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A131" s="2"/>
       <c r="B131" s="2"/>
       <c r="C131" s="2"/>
@@ -11305,7 +11305,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="132" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A132" s="2"/>
       <c r="B132" s="2"/>
       <c r="C132" s="2"/>
@@ -11350,7 +11350,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="133" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A133" s="2"/>
       <c r="B133" s="2"/>
       <c r="C133" s="2"/>
@@ -11395,7 +11395,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="134" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A134" s="2" t="s">
         <v>29</v>
       </c>
@@ -11484,7 +11484,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="135" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A135" s="2"/>
       <c r="B135" s="2"/>
       <c r="C135" s="2"/>
@@ -11529,7 +11529,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="136" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A136" s="2"/>
       <c r="B136" s="2"/>
       <c r="C136" s="2"/>
@@ -11574,7 +11574,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="137" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A137" s="2" t="s">
         <v>29</v>
       </c>
@@ -11663,7 +11663,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="138" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A138" s="2"/>
       <c r="B138" s="2"/>
       <c r="C138" s="2"/>
@@ -11708,7 +11708,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="139" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A139" s="2"/>
       <c r="B139" s="2"/>
       <c r="C139" s="2"/>
@@ -11753,7 +11753,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="140" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A140" s="2" t="s">
         <v>29</v>
       </c>
@@ -11842,7 +11842,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="141" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A141" s="2"/>
       <c r="B141" s="2"/>
       <c r="C141" s="2"/>
@@ -11887,7 +11887,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="142" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A142" s="2"/>
       <c r="B142" s="2"/>
       <c r="C142" s="2"/>
@@ -11932,7 +11932,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="143" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A143" s="2" t="s">
         <v>29</v>
       </c>
@@ -12021,7 +12021,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="144" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A144" s="2"/>
       <c r="B144" s="2"/>
       <c r="C144" s="2"/>
@@ -12066,7 +12066,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="145" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A145" s="2"/>
       <c r="B145" s="2"/>
       <c r="C145" s="2"/>
@@ -12111,7 +12111,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="146" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A146" s="2" t="s">
         <v>29</v>
       </c>
@@ -12200,7 +12200,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="147" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A147" s="2"/>
       <c r="B147" s="2"/>
       <c r="C147" s="2"/>
@@ -12245,7 +12245,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="148" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A148" s="2"/>
       <c r="B148" s="2"/>
       <c r="C148" s="2"/>
@@ -12290,7 +12290,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="149" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A149" s="2" t="s">
         <v>29</v>
       </c>
@@ -12379,7 +12379,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="150" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A150" s="2"/>
       <c r="B150" s="2"/>
       <c r="C150" s="2"/>
@@ -12424,7 +12424,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="151" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A151" s="2"/>
       <c r="B151" s="2"/>
       <c r="C151" s="2"/>
@@ -12469,7 +12469,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="152" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A152" s="2" t="s">
         <v>29</v>
       </c>
@@ -12558,7 +12558,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="153" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A153" s="2"/>
       <c r="B153" s="2"/>
       <c r="C153" s="2"/>
@@ -12603,7 +12603,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="154" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A154" s="2" t="s">
         <v>29</v>
       </c>
@@ -12688,7 +12688,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="155" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A155" s="2"/>
       <c r="B155" s="2"/>
       <c r="C155" s="2"/>
@@ -12733,7 +12733,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="156" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A156" s="2" t="s">
         <v>29</v>
       </c>
@@ -12822,7 +12822,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="157" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A157" s="2"/>
       <c r="B157" s="2"/>
       <c r="C157" s="2"/>
@@ -12867,7 +12867,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="158" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A158" s="2"/>
       <c r="B158" s="2"/>
       <c r="C158" s="2"/>
@@ -12912,7 +12912,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="159" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A159" s="2" t="s">
         <v>29</v>
       </c>
@@ -12997,7 +12997,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="160" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A160" s="2"/>
       <c r="B160" s="2"/>
       <c r="C160" s="2"/>
@@ -13042,7 +13042,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="161" spans="1:29" ht="45" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A161" s="2" t="s">
         <v>29</v>
       </c>
@@ -13131,7 +13131,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="162" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A162" s="2"/>
       <c r="B162" s="2"/>
       <c r="C162" s="2"/>
@@ -13176,7 +13176,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="163" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A163" s="2"/>
       <c r="B163" s="2"/>
       <c r="C163" s="2"/>
@@ -13221,7 +13221,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="164" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A164" s="2" t="s">
         <v>29</v>
       </c>
@@ -13310,7 +13310,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="165" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A165" s="2"/>
       <c r="B165" s="2"/>
       <c r="C165" s="2"/>
@@ -13359,7 +13359,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="166" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A166" s="2" t="s">
         <v>29</v>
       </c>
@@ -13444,7 +13444,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="167" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A167" s="2"/>
       <c r="B167" s="2"/>
       <c r="C167" s="2"/>
@@ -13489,7 +13489,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="168" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A168" s="2"/>
       <c r="B168" s="2"/>
       <c r="C168" s="2"/>
@@ -13534,7 +13534,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="169" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A169" s="2"/>
       <c r="B169" s="2"/>
       <c r="C169" s="2"/>
@@ -13579,7 +13579,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="170" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A170" s="2"/>
       <c r="B170" s="2"/>
       <c r="C170" s="2"/>
@@ -13624,7 +13624,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="171" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A171" s="2" t="s">
         <v>29</v>
       </c>
@@ -13709,7 +13709,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="172" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A172" s="2"/>
       <c r="B172" s="2"/>
       <c r="C172" s="2"/>
@@ -13754,7 +13754,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="173" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A173" s="2"/>
       <c r="B173" s="2"/>
       <c r="C173" s="2"/>
@@ -13799,7 +13799,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="174" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A174" s="2"/>
       <c r="B174" s="2"/>
       <c r="C174" s="2"/>
@@ -13844,7 +13844,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="175" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A175" s="2" t="s">
         <v>29</v>
       </c>
@@ -13907,7 +13907,7 @@
       <c r="AB175" s="2"/>
       <c r="AC175" s="2"/>
     </row>
-    <row r="176" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A176" s="2" t="s">
         <v>29</v>
       </c>
@@ -13990,7 +13990,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="177" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A177" s="2"/>
       <c r="B177" s="2"/>
       <c r="C177" s="2"/>
@@ -14035,7 +14035,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="178" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A178" s="2"/>
       <c r="B178" s="2"/>
       <c r="C178" s="2"/>
@@ -14080,7 +14080,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="179" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A179" s="2"/>
       <c r="B179" s="2"/>
       <c r="C179" s="2"/>
@@ -14125,7 +14125,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="180" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A180" s="2" t="s">
         <v>29</v>
       </c>
@@ -14208,7 +14208,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="181" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A181" s="2"/>
       <c r="B181" s="2"/>
       <c r="C181" s="2"/>
@@ -14253,7 +14253,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="182" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A182" s="2"/>
       <c r="B182" s="2"/>
       <c r="C182" s="2"/>
@@ -14298,7 +14298,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="183" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A183" s="2"/>
       <c r="B183" s="2"/>
       <c r="C183" s="2"/>
@@ -14343,7 +14343,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="184" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A184" s="2"/>
       <c r="B184" s="2"/>
       <c r="C184" s="2"/>
@@ -14388,7 +14388,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="185" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A185" s="2" t="s">
         <v>29</v>
       </c>
@@ -14453,7 +14453,7 @@
       <c r="AB185" s="2"/>
       <c r="AC185" s="2"/>
     </row>
-    <row r="186" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A186" s="2" t="s">
         <v>29</v>
       </c>
@@ -14518,7 +14518,7 @@
       <c r="AB186" s="2"/>
       <c r="AC186" s="2"/>
     </row>
-    <row r="187" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A187" s="2" t="s">
         <v>29</v>
       </c>
@@ -14583,7 +14583,7 @@
       <c r="AB187" s="2"/>
       <c r="AC187" s="2"/>
     </row>
-    <row r="188" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A188" s="2" t="s">
         <v>29</v>
       </c>
@@ -14648,7 +14648,7 @@
       <c r="AB188" s="2"/>
       <c r="AC188" s="2"/>
     </row>
-    <row r="189" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A189" s="2" t="s">
         <v>29</v>
       </c>
@@ -14713,7 +14713,7 @@
       <c r="AB189" s="2"/>
       <c r="AC189" s="2"/>
     </row>
-    <row r="190" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A190" s="2" t="s">
         <v>29</v>
       </c>
@@ -14778,7 +14778,7 @@
       <c r="AB190" s="2"/>
       <c r="AC190" s="2"/>
     </row>
-    <row r="191" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A191" s="2" t="s">
         <v>29</v>
       </c>
@@ -14867,7 +14867,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="192" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A192" s="2"/>
       <c r="B192" s="2"/>
       <c r="C192" s="2"/>
@@ -14916,7 +14916,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="193" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A193" s="2"/>
       <c r="B193" s="2"/>
       <c r="C193" s="2"/>
@@ -14961,7 +14961,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="194" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A194" s="2"/>
       <c r="B194" s="2"/>
       <c r="C194" s="2"/>
@@ -15006,7 +15006,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="195" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A195" s="2"/>
       <c r="B195" s="2"/>
       <c r="C195" s="2"/>
@@ -15051,7 +15051,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="196" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A196" s="2"/>
       <c r="B196" s="2"/>
       <c r="C196" s="2"/>
@@ -15096,7 +15096,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="197" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A197" s="2"/>
       <c r="B197" s="2"/>
       <c r="C197" s="2"/>
@@ -15141,7 +15141,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="198" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A198" s="2" t="s">
         <v>29</v>
       </c>
@@ -15230,7 +15230,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="199" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A199" s="2"/>
       <c r="B199" s="2"/>
       <c r="C199" s="2"/>
@@ -15279,7 +15279,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="200" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A200" s="2"/>
       <c r="B200" s="2"/>
       <c r="C200" s="2"/>
@@ -15328,7 +15328,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="201" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A201" s="2"/>
       <c r="B201" s="2"/>
       <c r="C201" s="2"/>
@@ -15373,7 +15373,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="202" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A202" s="2" t="s">
         <v>29</v>
       </c>
@@ -15462,7 +15462,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="203" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A203" s="2"/>
       <c r="B203" s="2"/>
       <c r="C203" s="2"/>
@@ -15511,7 +15511,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="204" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A204" s="2"/>
       <c r="B204" s="2"/>
       <c r="C204" s="2"/>
@@ -15556,7 +15556,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="205" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A205" s="2" t="s">
         <v>29</v>
       </c>
@@ -15645,7 +15645,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="206" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A206" s="2"/>
       <c r="B206" s="2"/>
       <c r="C206" s="2"/>
@@ -15690,7 +15690,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="207" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A207" s="2"/>
       <c r="B207" s="2"/>
       <c r="C207" s="2"/>
@@ -15735,7 +15735,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="208" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A208" s="2" t="s">
         <v>29</v>
       </c>
@@ -15824,7 +15824,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="209" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A209" s="2"/>
       <c r="B209" s="2"/>
       <c r="C209" s="2"/>
@@ -15873,7 +15873,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="210" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A210" s="2"/>
       <c r="B210" s="2"/>
       <c r="C210" s="2"/>
@@ -15918,7 +15918,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="211" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A211" s="2" t="s">
         <v>29</v>
       </c>
@@ -16007,7 +16007,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="212" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A212" s="2"/>
       <c r="B212" s="2"/>
       <c r="C212" s="2"/>
@@ -16056,7 +16056,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="213" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A213" s="2"/>
       <c r="B213" s="2"/>
       <c r="C213" s="2"/>
@@ -16105,7 +16105,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="214" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A214" s="2"/>
       <c r="B214" s="2"/>
       <c r="C214" s="2"/>
@@ -16154,7 +16154,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="215" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A215" s="2"/>
       <c r="B215" s="2"/>
       <c r="C215" s="2"/>
@@ -16203,7 +16203,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="216" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A216" s="2"/>
       <c r="B216" s="2"/>
       <c r="C216" s="2"/>
@@ -16248,7 +16248,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="217" spans="1:29" ht="75" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:29" ht="57" x14ac:dyDescent="0.45">
       <c r="A217" s="2" t="s">
         <v>29</v>
       </c>
@@ -16333,7 +16333,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="218" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A218" s="2"/>
       <c r="B218" s="2"/>
       <c r="C218" s="2"/>
@@ -16378,7 +16378,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="219" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A219" s="2"/>
       <c r="B219" s="2"/>
       <c r="C219" s="2"/>
@@ -16423,7 +16423,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="220" spans="1:29" ht="45" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A220" s="2" t="s">
         <v>29</v>
       </c>
@@ -16512,7 +16512,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="221" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A221" s="2"/>
       <c r="B221" s="2"/>
       <c r="C221" s="2"/>
@@ -16557,7 +16557,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="222" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A222" s="2" t="s">
         <v>29</v>
       </c>
@@ -16646,7 +16646,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="223" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A223" s="2"/>
       <c r="B223" s="2"/>
       <c r="C223" s="2"/>
@@ -16695,7 +16695,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="224" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A224" s="2"/>
       <c r="B224" s="2"/>
       <c r="C224" s="2"/>
@@ -16744,7 +16744,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="225" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A225" s="2" t="s">
         <v>29</v>
       </c>
@@ -16829,7 +16829,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="226" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A226" s="2"/>
       <c r="B226" s="2"/>
       <c r="C226" s="2"/>
@@ -16874,7 +16874,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="227" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A227" s="2"/>
       <c r="B227" s="2"/>
       <c r="C227" s="2"/>
@@ -16919,7 +16919,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="228" spans="1:29" ht="45" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:29" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A228" s="2" t="s">
         <v>29</v>
       </c>
@@ -17008,7 +17008,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="229" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A229" s="2"/>
       <c r="B229" s="2"/>
       <c r="C229" s="2"/>
@@ -17057,7 +17057,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="230" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A230" s="2"/>
       <c r="B230" s="2"/>
       <c r="C230" s="2"/>
@@ -17106,7 +17106,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="231" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A231" s="2"/>
       <c r="B231" s="2"/>
       <c r="C231" s="2"/>
@@ -17151,7 +17151,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="232" spans="1:29" ht="45" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A232" s="2"/>
       <c r="B232" s="2"/>
       <c r="C232" s="2"/>
@@ -17196,7 +17196,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="233" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A233" s="2" t="s">
         <v>29</v>
       </c>
@@ -17281,7 +17281,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="234" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A234" s="2"/>
       <c r="B234" s="2"/>
       <c r="C234" s="2"/>
@@ -17326,7 +17326,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="235" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A235" s="2"/>
       <c r="B235" s="2"/>
       <c r="C235" s="2"/>
@@ -17371,7 +17371,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="236" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A236" s="2" t="s">
         <v>29</v>
       </c>
@@ -17460,7 +17460,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="237" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A237" s="2"/>
       <c r="B237" s="2"/>
       <c r="C237" s="2"/>
@@ -17505,7 +17505,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="238" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A238" s="2"/>
       <c r="B238" s="2"/>
       <c r="C238" s="2"/>
@@ -17550,7 +17550,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="239" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A239" s="2"/>
       <c r="B239" s="2"/>
       <c r="C239" s="2"/>
@@ -17595,7 +17595,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="240" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A240" s="2" t="s">
         <v>29</v>
       </c>
@@ -17682,7 +17682,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="241" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A241" s="2"/>
       <c r="B241" s="2"/>
       <c r="C241" s="2"/>
@@ -17727,7 +17727,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="242" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A242" s="2"/>
       <c r="B242" s="2"/>
       <c r="C242" s="2"/>
@@ -17772,7 +17772,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="243" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A243" s="2"/>
       <c r="B243" s="2"/>
       <c r="C243" s="2"/>
@@ -17817,7 +17817,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="244" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A244" s="2"/>
       <c r="B244" s="2"/>
       <c r="C244" s="2"/>
@@ -17862,7 +17862,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="245" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A245" s="2" t="s">
         <v>29</v>
       </c>
@@ -17951,7 +17951,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="246" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A246" s="2"/>
       <c r="B246" s="2"/>
       <c r="C246" s="2"/>
@@ -17996,7 +17996,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="247" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A247" s="2"/>
       <c r="B247" s="2"/>
       <c r="C247" s="2"/>
@@ -18041,7 +18041,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="248" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A248" s="2"/>
       <c r="B248" s="2"/>
       <c r="C248" s="2"/>
@@ -18086,7 +18086,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="249" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A249" s="2"/>
       <c r="B249" s="2"/>
       <c r="C249" s="2"/>
@@ -18131,7 +18131,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="250" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A250" s="2"/>
       <c r="B250" s="2"/>
       <c r="C250" s="2"/>
@@ -18176,7 +18176,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="251" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A251" s="2" t="s">
         <v>29</v>
       </c>
@@ -18265,7 +18265,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="252" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A252" s="2"/>
       <c r="B252" s="2"/>
       <c r="C252" s="2"/>
@@ -18310,7 +18310,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="253" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A253" s="2"/>
       <c r="B253" s="2"/>
       <c r="C253" s="2"/>
@@ -18355,7 +18355,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="254" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A254" s="2"/>
       <c r="B254" s="2"/>
       <c r="C254" s="2"/>
@@ -18400,7 +18400,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="255" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A255" s="2"/>
       <c r="B255" s="2"/>
       <c r="C255" s="2"/>
@@ -18445,7 +18445,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="256" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A256" s="2" t="s">
         <v>29</v>
       </c>
@@ -18508,7 +18508,7 @@
       <c r="AB256" s="2"/>
       <c r="AC256" s="2"/>
     </row>
-    <row r="257" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A257" s="2" t="s">
         <v>29</v>
       </c>
@@ -18571,7 +18571,7 @@
       <c r="AB257" s="2"/>
       <c r="AC257" s="2"/>
     </row>
-    <row r="258" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A258" s="2" t="s">
         <v>29</v>
       </c>
@@ -18634,7 +18634,7 @@
       <c r="AB258" s="2"/>
       <c r="AC258" s="2"/>
     </row>
-    <row r="259" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A259" s="2" t="s">
         <v>29</v>
       </c>
@@ -18697,7 +18697,7 @@
       <c r="AB259" s="2"/>
       <c r="AC259" s="2"/>
     </row>
-    <row r="260" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A260" s="2" t="s">
         <v>29</v>
       </c>
@@ -18760,7 +18760,7 @@
       <c r="AB260" s="2"/>
       <c r="AC260" s="2"/>
     </row>
-    <row r="261" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A261" s="2" t="s">
         <v>29</v>
       </c>
@@ -18845,7 +18845,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="262" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A262" s="2"/>
       <c r="B262" s="2"/>
       <c r="C262" s="2"/>
@@ -18890,7 +18890,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="263" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A263" s="2"/>
       <c r="B263" s="2"/>
       <c r="C263" s="2"/>
@@ -18935,7 +18935,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="264" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A264" s="2" t="s">
         <v>29</v>
       </c>
@@ -19024,7 +19024,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="265" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A265" s="2"/>
       <c r="B265" s="2"/>
       <c r="C265" s="2"/>
@@ -19069,7 +19069,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="266" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A266" s="2" t="s">
         <v>29</v>
       </c>
@@ -19158,7 +19158,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="267" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A267" s="2"/>
       <c r="B267" s="2"/>
       <c r="C267" s="2"/>
@@ -19203,7 +19203,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="268" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A268" s="2"/>
       <c r="B268" s="2"/>
       <c r="C268" s="2"/>
@@ -19248,7 +19248,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="269" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A269" s="2" t="s">
         <v>29</v>
       </c>
@@ -19337,7 +19337,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="270" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A270" s="2"/>
       <c r="B270" s="2"/>
       <c r="C270" s="2"/>
@@ -19382,7 +19382,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="271" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A271" s="2"/>
       <c r="B271" s="2"/>
       <c r="C271" s="2"/>
@@ -19427,7 +19427,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="272" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A272" s="2" t="s">
         <v>29</v>
       </c>
@@ -19516,7 +19516,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="273" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A273" s="2"/>
       <c r="B273" s="2"/>
       <c r="C273" s="2"/>
@@ -19561,7 +19561,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="274" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A274" s="2"/>
       <c r="B274" s="2"/>
       <c r="C274" s="2"/>
@@ -19606,7 +19606,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="275" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A275" s="2" t="s">
         <v>29</v>
       </c>
@@ -19695,7 +19695,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="276" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A276" s="2"/>
       <c r="B276" s="2"/>
       <c r="C276" s="2"/>
@@ -19740,7 +19740,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="277" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A277" s="2"/>
       <c r="B277" s="2"/>
       <c r="C277" s="2"/>
@@ -19785,7 +19785,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="278" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A278" s="2"/>
       <c r="B278" s="2"/>
       <c r="C278" s="2"/>
@@ -19830,7 +19830,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="279" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A279" s="2" t="s">
         <v>29</v>
       </c>
@@ -19919,7 +19919,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="280" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A280" s="2"/>
       <c r="B280" s="2"/>
       <c r="C280" s="2"/>
@@ -19968,7 +19968,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="281" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A281" s="2"/>
       <c r="B281" s="2"/>
       <c r="C281" s="2"/>
@@ -20017,7 +20017,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="282" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A282" s="2"/>
       <c r="B282" s="2"/>
       <c r="C282" s="2"/>
@@ -20062,7 +20062,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="283" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A283" s="2" t="s">
         <v>29</v>
       </c>
@@ -20151,7 +20151,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="284" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A284" s="2"/>
       <c r="B284" s="2"/>
       <c r="C284" s="2"/>
@@ -20200,7 +20200,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="285" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A285" s="2"/>
       <c r="B285" s="2"/>
       <c r="C285" s="2"/>
@@ -20245,7 +20245,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="286" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A286" s="2" t="s">
         <v>29</v>
       </c>
@@ -20334,7 +20334,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="287" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A287" s="2"/>
       <c r="B287" s="2"/>
       <c r="C287" s="2"/>
@@ -20383,7 +20383,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="288" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A288" s="2"/>
       <c r="B288" s="2"/>
       <c r="C288" s="2"/>
@@ -20428,7 +20428,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="289" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A289" s="2" t="s">
         <v>29</v>
       </c>
@@ -20517,7 +20517,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="290" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A290" s="2"/>
       <c r="B290" s="2"/>
       <c r="C290" s="2"/>
@@ -20562,7 +20562,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="291" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A291" s="2"/>
       <c r="B291" s="2"/>
       <c r="C291" s="2"/>
@@ -20607,7 +20607,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="292" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A292" s="2" t="s">
         <v>29</v>
       </c>
@@ -20696,7 +20696,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="293" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A293" s="2"/>
       <c r="B293" s="2"/>
       <c r="C293" s="2"/>
@@ -20741,7 +20741,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="294" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A294" s="2"/>
       <c r="B294" s="2"/>
       <c r="C294" s="2"/>
@@ -20786,7 +20786,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="295" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A295" s="2"/>
       <c r="B295" s="2"/>
       <c r="C295" s="2"/>
@@ -20831,7 +20831,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="296" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A296" s="2" t="s">
         <v>29</v>
       </c>
@@ -20920,7 +20920,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="297" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A297" s="2"/>
       <c r="B297" s="2"/>
       <c r="C297" s="2"/>
@@ -20969,7 +20969,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="298" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A298" s="2"/>
       <c r="B298" s="2"/>
       <c r="C298" s="2"/>
@@ -21014,7 +21014,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="299" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A299" s="2" t="s">
         <v>29</v>
       </c>
@@ -21103,7 +21103,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="300" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A300" s="2"/>
       <c r="B300" s="2"/>
       <c r="C300" s="2"/>
@@ -21148,7 +21148,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="301" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A301" s="2"/>
       <c r="B301" s="2"/>
       <c r="C301" s="2"/>
@@ -21193,7 +21193,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="302" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A302" s="2" t="s">
         <v>29</v>
       </c>
@@ -21282,7 +21282,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="303" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A303" s="2"/>
       <c r="B303" s="2"/>
       <c r="C303" s="2"/>
@@ -21327,7 +21327,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="304" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A304" s="2"/>
       <c r="B304" s="2"/>
       <c r="C304" s="2"/>
@@ -21372,7 +21372,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="305" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A305" s="2" t="s">
         <v>29</v>
       </c>
@@ -21461,7 +21461,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="306" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A306" s="2"/>
       <c r="B306" s="2"/>
       <c r="C306" s="2"/>
@@ -21510,7 +21510,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="307" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A307" s="2"/>
       <c r="B307" s="2"/>
       <c r="C307" s="2"/>
@@ -21555,7 +21555,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="308" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A308" s="2" t="s">
         <v>29</v>
       </c>
@@ -21644,7 +21644,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="309" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A309" s="2"/>
       <c r="B309" s="2"/>
       <c r="C309" s="2"/>
@@ -21689,7 +21689,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="310" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A310" s="2"/>
       <c r="B310" s="2"/>
       <c r="C310" s="2"/>
@@ -21734,7 +21734,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="311" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A311" s="2"/>
       <c r="B311" s="2"/>
       <c r="C311" s="2"/>
@@ -21779,7 +21779,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="312" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A312" s="2"/>
       <c r="B312" s="2"/>
       <c r="C312" s="2"/>
@@ -21824,7 +21824,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="313" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A313" s="2"/>
       <c r="B313" s="2"/>
       <c r="C313" s="2"/>
@@ -21869,7 +21869,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="314" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A314" s="2"/>
       <c r="B314" s="2"/>
       <c r="C314" s="2"/>
@@ -21914,7 +21914,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="315" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A315" s="2" t="s">
         <v>29</v>
       </c>
@@ -21999,7 +21999,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="316" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A316" s="2"/>
       <c r="B316" s="2"/>
       <c r="C316" s="2"/>
@@ -22044,7 +22044,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="317" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A317" s="2"/>
       <c r="B317" s="2"/>
       <c r="C317" s="2"/>
@@ -22089,7 +22089,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="318" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A318" s="2"/>
       <c r="B318" s="2"/>
       <c r="C318" s="2"/>
@@ -22134,7 +22134,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="319" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A319" s="2"/>
       <c r="B319" s="2"/>
       <c r="C319" s="2"/>
@@ -22179,7 +22179,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="320" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A320" s="2" t="s">
         <v>29</v>
       </c>
@@ -22268,7 +22268,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="321" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A321" s="2"/>
       <c r="B321" s="2"/>
       <c r="C321" s="2"/>
@@ -22305,7 +22305,7 @@
       <c r="AB321" s="2"/>
       <c r="AC321" s="2"/>
     </row>
-    <row r="322" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A322" s="2"/>
       <c r="B322" s="2"/>
       <c r="C322" s="2"/>
@@ -22354,7 +22354,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="323" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A323" s="2"/>
       <c r="B323" s="2"/>
       <c r="C323" s="2"/>
@@ -22403,7 +22403,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="324" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A324" s="2"/>
       <c r="B324" s="2"/>
       <c r="C324" s="2"/>
@@ -22452,7 +22452,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="325" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A325" s="2" t="s">
         <v>29</v>
       </c>
@@ -22541,7 +22541,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="326" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A326" s="2"/>
       <c r="B326" s="2"/>
       <c r="C326" s="2"/>
@@ -22578,7 +22578,7 @@
       <c r="AB326" s="2"/>
       <c r="AC326" s="2"/>
     </row>
-    <row r="327" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A327" s="2"/>
       <c r="B327" s="2"/>
       <c r="C327" s="2"/>
@@ -22627,7 +22627,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="328" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A328" s="2"/>
       <c r="B328" s="2"/>
       <c r="C328" s="2"/>
@@ -22676,7 +22676,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="329" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A329" s="2"/>
       <c r="B329" s="2"/>
       <c r="C329" s="2"/>
@@ -22725,7 +22725,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="330" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A330" s="2" t="s">
         <v>29</v>
       </c>
@@ -22814,7 +22814,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="331" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A331" s="2"/>
       <c r="B331" s="2"/>
       <c r="C331" s="2"/>
@@ -22859,7 +22859,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="332" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A332" s="2" t="s">
         <v>29</v>
       </c>
@@ -22948,7 +22948,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="333" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A333" s="2"/>
       <c r="B333" s="2"/>
       <c r="C333" s="2"/>
@@ -22993,7 +22993,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="334" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A334" s="2"/>
       <c r="B334" s="2"/>
       <c r="C334" s="2"/>
@@ -23038,7 +23038,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="335" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A335" s="2" t="s">
         <v>29</v>
       </c>
@@ -23127,7 +23127,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="336" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A336" s="2"/>
       <c r="B336" s="2"/>
       <c r="C336" s="2"/>
@@ -23172,7 +23172,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="337" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A337" s="2" t="s">
         <v>29</v>
       </c>
@@ -23261,7 +23261,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="338" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A338" s="2"/>
       <c r="B338" s="2"/>
       <c r="C338" s="2"/>
@@ -23306,7 +23306,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="339" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A339" s="2" t="s">
         <v>29</v>
       </c>
@@ -23395,7 +23395,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="340" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A340" s="2"/>
       <c r="B340" s="2"/>
       <c r="C340" s="2"/>
@@ -23440,7 +23440,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="341" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A341" s="2" t="s">
         <v>29</v>
       </c>
@@ -23529,7 +23529,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="342" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A342" s="2"/>
       <c r="B342" s="2"/>
       <c r="C342" s="2"/>
@@ -23574,7 +23574,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="343" spans="1:29" ht="45" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:29" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A343" s="2" t="s">
         <v>29</v>
       </c>
@@ -23663,7 +23663,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="344" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A344" s="2"/>
       <c r="B344" s="2"/>
       <c r="C344" s="2"/>
@@ -23712,7 +23712,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="345" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A345" s="2" t="s">
         <v>29</v>
       </c>
@@ -23801,7 +23801,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="346" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A346" s="2"/>
       <c r="B346" s="2"/>
       <c r="C346" s="2"/>
@@ -23846,7 +23846,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="347" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A347" s="2"/>
       <c r="B347" s="2"/>
       <c r="C347" s="2"/>
@@ -23891,7 +23891,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="348" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A348" s="2"/>
       <c r="B348" s="2"/>
       <c r="C348" s="2"/>
@@ -23936,7 +23936,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="349" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A349" s="2"/>
       <c r="B349" s="2"/>
       <c r="C349" s="2"/>
@@ -23981,7 +23981,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="350" spans="1:29" ht="45" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:29" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A350" s="2" t="s">
         <v>29</v>
       </c>
@@ -24070,7 +24070,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="351" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A351" s="2"/>
       <c r="B351" s="2"/>
       <c r="C351" s="2"/>
@@ -24119,7 +24119,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="352" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A352" s="2"/>
       <c r="B352" s="2"/>
       <c r="C352" s="2"/>
@@ -24168,7 +24168,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="353" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A353" s="2"/>
       <c r="B353" s="2"/>
       <c r="C353" s="2"/>
@@ -24217,7 +24217,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="354" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A354" s="2" t="s">
         <v>29</v>
       </c>
@@ -24302,7 +24302,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="355" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A355" s="2"/>
       <c r="B355" s="2"/>
       <c r="C355" s="2"/>
@@ -24351,7 +24351,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="356" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A356" s="2"/>
       <c r="B356" s="2"/>
       <c r="C356" s="2"/>
@@ -24396,7 +24396,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="357" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A357" s="2"/>
       <c r="B357" s="2"/>
       <c r="C357" s="2"/>
@@ -24441,7 +24441,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="358" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A358" s="2"/>
       <c r="B358" s="2"/>
       <c r="C358" s="2"/>
@@ -24486,7 +24486,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="359" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A359" s="2"/>
       <c r="B359" s="2"/>
       <c r="C359" s="2"/>
@@ -24531,7 +24531,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="360" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A360" s="2" t="s">
         <v>29</v>
       </c>
@@ -24620,7 +24620,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="361" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A361" s="2"/>
       <c r="B361" s="2"/>
       <c r="C361" s="2"/>
@@ -24669,7 +24669,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="362" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A362" s="2"/>
       <c r="B362" s="2"/>
       <c r="C362" s="2"/>
@@ -24718,7 +24718,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="363" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A363" s="2"/>
       <c r="B363" s="2"/>
       <c r="C363" s="2"/>
@@ -24767,7 +24767,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="364" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A364" s="2" t="s">
         <v>29</v>
       </c>
@@ -24852,7 +24852,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="365" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A365" s="2"/>
       <c r="B365" s="2"/>
       <c r="C365" s="2"/>
@@ -24901,7 +24901,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="366" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A366" s="2"/>
       <c r="B366" s="2"/>
       <c r="C366" s="2"/>
@@ -24946,7 +24946,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="367" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A367" s="2"/>
       <c r="B367" s="2"/>
       <c r="C367" s="2"/>
@@ -24991,7 +24991,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="368" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A368" s="2"/>
       <c r="B368" s="2"/>
       <c r="C368" s="2"/>
@@ -25036,7 +25036,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="369" spans="1:29" ht="45" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A369" s="2" t="s">
         <v>29</v>
       </c>
@@ -25125,7 +25125,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="370" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A370" s="2"/>
       <c r="B370" s="2"/>
       <c r="C370" s="2"/>
@@ -25170,7 +25170,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="371" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A371" s="2"/>
       <c r="B371" s="2"/>
       <c r="C371" s="2"/>
@@ -25215,7 +25215,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="372" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A372" s="2"/>
       <c r="B372" s="2"/>
       <c r="C372" s="2"/>
@@ -25260,7 +25260,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="373" spans="1:29" ht="45" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A373" s="2" t="s">
         <v>29</v>
       </c>
@@ -25349,7 +25349,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="374" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A374" s="2"/>
       <c r="B374" s="2"/>
       <c r="C374" s="2"/>
@@ -25394,7 +25394,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="375" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A375" s="2"/>
       <c r="B375" s="2"/>
       <c r="C375" s="2"/>
@@ -25439,7 +25439,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="376" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A376" s="2"/>
       <c r="B376" s="2"/>
       <c r="C376" s="2"/>
@@ -25484,7 +25484,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="377" spans="1:29" ht="45" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A377" s="2" t="s">
         <v>29</v>
       </c>
@@ -25573,7 +25573,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="378" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A378" s="2"/>
       <c r="B378" s="2"/>
       <c r="C378" s="2"/>
@@ -25618,7 +25618,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="379" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A379" s="2"/>
       <c r="B379" s="2"/>
       <c r="C379" s="2"/>
@@ -25663,7 +25663,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="380" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A380" s="2"/>
       <c r="B380" s="2"/>
       <c r="C380" s="2"/>
@@ -25708,7 +25708,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="381" spans="1:29" ht="45" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:29" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A381" s="2" t="s">
         <v>29</v>
       </c>
@@ -25797,7 +25797,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="382" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A382" s="2"/>
       <c r="B382" s="2"/>
       <c r="C382" s="2"/>
@@ -25842,7 +25842,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="383" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A383" s="2" t="s">
         <v>29</v>
       </c>
@@ -25927,7 +25927,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="384" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A384" s="2"/>
       <c r="B384" s="2"/>
       <c r="C384" s="2"/>
@@ -25972,7 +25972,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="385" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A385" s="2"/>
       <c r="B385" s="2"/>
       <c r="C385" s="2"/>
@@ -26017,7 +26017,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="386" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A386" s="2"/>
       <c r="B386" s="2"/>
       <c r="C386" s="2"/>
@@ -26062,7 +26062,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="387" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A387" s="2"/>
       <c r="B387" s="2"/>
       <c r="C387" s="2"/>
@@ -26107,7 +26107,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="388" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A388" s="2" t="s">
         <v>29</v>
       </c>
@@ -26192,7 +26192,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="389" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A389" s="2"/>
       <c r="B389" s="2"/>
       <c r="C389" s="2"/>
@@ -26237,7 +26237,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="390" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A390" s="2"/>
       <c r="B390" s="2"/>
       <c r="C390" s="2"/>
@@ -26282,7 +26282,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="391" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A391" s="2"/>
       <c r="B391" s="2"/>
       <c r="C391" s="2"/>
@@ -26327,7 +26327,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="392" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A392" s="2"/>
       <c r="B392" s="2"/>
       <c r="C392" s="2"/>
@@ -26372,7 +26372,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="393" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A393" s="2"/>
       <c r="B393" s="2"/>
       <c r="C393" s="2"/>
@@ -26417,7 +26417,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="394" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A394" s="2" t="s">
         <v>29</v>
       </c>
@@ -26502,7 +26502,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="395" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A395" s="2"/>
       <c r="B395" s="2"/>
       <c r="C395" s="2"/>
@@ -26547,7 +26547,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="396" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A396" s="2"/>
       <c r="B396" s="2"/>
       <c r="C396" s="2"/>
@@ -26592,7 +26592,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="397" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A397" s="2" t="s">
         <v>29</v>
       </c>
@@ -26677,7 +26677,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="398" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A398" s="2" t="s">
         <v>29</v>
       </c>
@@ -26762,7 +26762,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="399" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A399" s="2"/>
       <c r="B399" s="2"/>
       <c r="C399" s="2"/>
@@ -26807,7 +26807,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="400" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A400" s="2"/>
       <c r="B400" s="2"/>
       <c r="C400" s="2"/>
@@ -26852,7 +26852,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="401" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A401" s="2" t="s">
         <v>29</v>
       </c>
@@ -26941,7 +26941,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="402" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A402" s="2"/>
       <c r="B402" s="2"/>
       <c r="C402" s="2"/>
@@ -26986,7 +26986,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="403" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A403" s="2"/>
       <c r="B403" s="2"/>
       <c r="C403" s="2"/>
@@ -27031,7 +27031,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="404" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A404" s="2"/>
       <c r="B404" s="2"/>
       <c r="C404" s="2"/>
@@ -27076,7 +27076,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="405" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A405" s="2"/>
       <c r="B405" s="2"/>
       <c r="C405" s="2"/>
@@ -27121,7 +27121,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="406" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A406" s="2"/>
       <c r="B406" s="2"/>
       <c r="C406" s="2"/>
@@ -27166,7 +27166,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="407" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A407" s="2" t="s">
         <v>29</v>
       </c>
@@ -27251,7 +27251,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="408" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A408" s="2"/>
       <c r="B408" s="2"/>
       <c r="C408" s="2"/>
@@ -27296,7 +27296,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="409" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A409" s="2"/>
       <c r="B409" s="2"/>
       <c r="C409" s="2"/>
@@ -27341,7 +27341,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="410" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A410" s="2"/>
       <c r="B410" s="2"/>
       <c r="C410" s="2"/>
@@ -27386,7 +27386,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="411" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A411" s="2"/>
       <c r="B411" s="2"/>
       <c r="C411" s="2"/>
@@ -27431,7 +27431,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="412" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A412" s="2"/>
       <c r="B412" s="2"/>
       <c r="C412" s="2"/>
@@ -27476,7 +27476,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="413" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A413" s="2"/>
       <c r="B413" s="2"/>
       <c r="C413" s="2"/>
@@ -27521,7 +27521,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="414" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A414" s="2" t="s">
         <v>29</v>
       </c>
@@ -27610,7 +27610,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="415" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A415" s="2"/>
       <c r="B415" s="2"/>
       <c r="C415" s="2"/>
@@ -27659,7 +27659,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="416" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A416" s="2" t="s">
         <v>29</v>
       </c>
@@ -27748,7 +27748,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="417" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A417" s="2"/>
       <c r="B417" s="2"/>
       <c r="C417" s="2"/>
@@ -27797,7 +27797,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="418" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A418" s="2"/>
       <c r="B418" s="2"/>
       <c r="C418" s="2"/>
@@ -27846,7 +27846,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="419" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A419" s="2"/>
       <c r="B419" s="2"/>
       <c r="C419" s="2"/>
@@ -27895,7 +27895,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="420" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A420" s="2" t="s">
         <v>29</v>
       </c>
@@ -27980,7 +27980,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="421" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A421" s="2"/>
       <c r="B421" s="2"/>
       <c r="C421" s="2"/>
@@ -28029,7 +28029,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="422" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A422" s="2"/>
       <c r="B422" s="2"/>
       <c r="C422" s="2"/>
@@ -28074,7 +28074,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="423" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A423" s="2"/>
       <c r="B423" s="2"/>
       <c r="C423" s="2"/>
@@ -28119,7 +28119,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="424" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A424" s="2"/>
       <c r="B424" s="2"/>
       <c r="C424" s="2"/>
@@ -28164,7 +28164,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="425" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A425" s="2"/>
       <c r="B425" s="2"/>
       <c r="C425" s="2"/>
@@ -28209,7 +28209,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="426" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A426" s="2" t="s">
         <v>29</v>
       </c>
@@ -28294,7 +28294,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="427" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A427" s="2"/>
       <c r="B427" s="2"/>
       <c r="C427" s="2"/>
@@ -28339,7 +28339,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="428" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A428" s="2"/>
       <c r="B428" s="2"/>
       <c r="C428" s="2"/>
@@ -28384,7 +28384,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="429" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A429" s="2" t="s">
         <v>29</v>
       </c>
@@ -28469,7 +28469,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="430" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A430" s="2"/>
       <c r="B430" s="2"/>
       <c r="C430" s="2"/>
@@ -28514,7 +28514,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="431" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A431" s="2"/>
       <c r="B431" s="2"/>
       <c r="C431" s="2"/>
@@ -28559,7 +28559,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="432" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A432" s="2" t="s">
         <v>29</v>
       </c>
@@ -28648,7 +28648,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="433" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A433" s="2"/>
       <c r="B433" s="2"/>
       <c r="C433" s="2"/>
@@ -28697,7 +28697,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="434" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A434" s="2"/>
       <c r="B434" s="2"/>
       <c r="C434" s="2"/>
@@ -28746,7 +28746,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="435" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A435" s="2"/>
       <c r="B435" s="2"/>
       <c r="C435" s="2"/>
@@ -28795,7 +28795,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="436" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A436" s="2"/>
       <c r="B436" s="2"/>
       <c r="C436" s="2"/>
@@ -28844,7 +28844,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="437" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A437" s="2" t="s">
         <v>29</v>
       </c>
@@ -28933,7 +28933,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="438" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A438" s="2"/>
       <c r="B438" s="2"/>
       <c r="C438" s="2"/>
@@ -28982,7 +28982,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="439" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A439" s="2"/>
       <c r="B439" s="2"/>
       <c r="C439" s="2"/>
@@ -29031,7 +29031,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="440" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A440" s="2"/>
       <c r="B440" s="2"/>
       <c r="C440" s="2"/>
@@ -29080,7 +29080,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="441" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A441" s="2"/>
       <c r="B441" s="2"/>
       <c r="C441" s="2"/>
@@ -29129,7 +29129,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="442" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A442" s="2"/>
       <c r="B442" s="2"/>
       <c r="C442" s="2"/>
@@ -29178,7 +29178,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="443" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A443" s="2" t="s">
         <v>29</v>
       </c>
@@ -29267,7 +29267,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="444" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A444" s="2"/>
       <c r="B444" s="2"/>
       <c r="C444" s="2"/>
@@ -29316,7 +29316,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="445" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A445" s="2"/>
       <c r="B445" s="2"/>
       <c r="C445" s="2"/>
@@ -29365,7 +29365,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="446" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A446" s="2"/>
       <c r="B446" s="2"/>
       <c r="C446" s="2"/>
@@ -29414,7 +29414,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="447" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A447" s="2"/>
       <c r="B447" s="2"/>
       <c r="C447" s="2"/>
@@ -29463,7 +29463,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="448" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A448" s="2"/>
       <c r="B448" s="2"/>
       <c r="C448" s="2"/>
@@ -29512,7 +29512,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="449" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A449" s="2" t="s">
         <v>29</v>
       </c>
@@ -29601,7 +29601,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="450" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A450" s="2"/>
       <c r="B450" s="2"/>
       <c r="C450" s="2"/>
@@ -29650,7 +29650,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="451" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A451" s="2"/>
       <c r="B451" s="2"/>
       <c r="C451" s="2"/>
@@ -29699,7 +29699,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="452" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A452" s="2"/>
       <c r="B452" s="2"/>
       <c r="C452" s="2"/>
@@ -29748,7 +29748,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="453" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A453" s="2"/>
       <c r="B453" s="2"/>
       <c r="C453" s="2"/>
@@ -29797,7 +29797,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="454" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A454" s="2"/>
       <c r="B454" s="2"/>
       <c r="C454" s="2"/>
@@ -29842,7 +29842,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="455" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A455" s="2" t="s">
         <v>29</v>
       </c>
@@ -29927,7 +29927,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="456" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A456" s="2"/>
       <c r="B456" s="2"/>
       <c r="C456" s="2"/>
@@ -29972,7 +29972,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="457" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A457" s="2"/>
       <c r="B457" s="2"/>
       <c r="C457" s="2"/>
@@ -30017,7 +30017,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="458" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A458" s="2"/>
       <c r="B458" s="2"/>
       <c r="C458" s="2"/>
@@ -30062,7 +30062,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="459" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A459" s="2"/>
       <c r="B459" s="2"/>
       <c r="C459" s="2"/>
@@ -30107,7 +30107,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="460" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A460" s="2"/>
       <c r="B460" s="2"/>
       <c r="C460" s="2"/>
@@ -30152,7 +30152,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="461" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A461" s="2" t="s">
         <v>29</v>
       </c>
@@ -30241,7 +30241,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="462" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A462" s="2"/>
       <c r="B462" s="2"/>
       <c r="C462" s="2"/>
@@ -30286,7 +30286,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="463" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A463" s="2"/>
       <c r="B463" s="2"/>
       <c r="C463" s="2"/>
@@ -30331,7 +30331,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="464" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A464" s="2" t="s">
         <v>29</v>
       </c>
@@ -30420,7 +30420,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="465" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A465" s="2"/>
       <c r="B465" s="2"/>
       <c r="C465" s="2"/>
@@ -30465,7 +30465,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="466" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A466" s="2" t="s">
         <v>29</v>
       </c>
@@ -30554,7 +30554,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="467" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A467" s="2"/>
       <c r="B467" s="2"/>
       <c r="C467" s="2"/>
@@ -30599,7 +30599,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="468" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A468" s="2" t="s">
         <v>29</v>
       </c>
@@ -30688,7 +30688,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="469" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A469" s="2"/>
       <c r="B469" s="2"/>
       <c r="C469" s="2"/>
@@ -30733,7 +30733,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="470" spans="1:29" ht="45" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:29" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A470" s="2" t="s">
         <v>29</v>
       </c>
@@ -30822,7 +30822,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="471" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A471" s="2"/>
       <c r="B471" s="2"/>
       <c r="C471" s="2"/>
@@ -30867,7 +30867,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="472" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A472" s="2"/>
       <c r="B472" s="2"/>
       <c r="C472" s="2"/>
@@ -30912,7 +30912,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="473" spans="1:29" ht="45" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A473" s="2" t="s">
         <v>29</v>
       </c>
@@ -31001,7 +31001,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="474" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A474" s="2"/>
       <c r="B474" s="2"/>
       <c r="C474" s="2"/>
@@ -31046,7 +31046,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="475" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A475" s="2"/>
       <c r="B475" s="2"/>
       <c r="C475" s="2"/>
@@ -31091,7 +31091,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="476" spans="1:29" ht="45" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A476" s="2" t="s">
         <v>29</v>
       </c>
@@ -31180,7 +31180,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="477" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A477" s="2"/>
       <c r="B477" s="2"/>
       <c r="C477" s="2"/>
@@ -31225,7 +31225,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="478" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A478" s="2"/>
       <c r="B478" s="2"/>
       <c r="C478" s="2"/>
@@ -31270,7 +31270,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="479" spans="1:29" ht="45" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:29" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A479" s="2" t="s">
         <v>29</v>
       </c>
@@ -31359,7 +31359,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="480" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A480" s="2"/>
       <c r="B480" s="2"/>
       <c r="C480" s="2"/>
@@ -31404,7 +31404,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="481" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A481" s="2"/>
       <c r="B481" s="2"/>
       <c r="C481" s="2"/>
@@ -31449,7 +31449,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="482" spans="1:29" ht="45" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:29" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A482" s="2" t="s">
         <v>29</v>
       </c>
@@ -31538,7 +31538,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="483" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A483" s="2"/>
       <c r="B483" s="2"/>
       <c r="C483" s="2"/>
@@ -31583,7 +31583,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="484" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A484" s="2"/>
       <c r="B484" s="2"/>
       <c r="C484" s="2"/>
@@ -31628,7 +31628,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="485" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A485" s="2" t="s">
         <v>29</v>
       </c>
@@ -31717,7 +31717,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="486" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A486" s="2"/>
       <c r="B486" s="2"/>
       <c r="C486" s="2"/>
@@ -31762,7 +31762,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="487" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A487" s="2"/>
       <c r="B487" s="2"/>
       <c r="C487" s="2"/>
@@ -31807,7 +31807,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="488" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A488" s="2" t="s">
         <v>29</v>
       </c>
@@ -31896,7 +31896,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="489" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A489" s="2"/>
       <c r="B489" s="2"/>
       <c r="C489" s="2"/>
@@ -31941,7 +31941,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="490" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A490" s="2"/>
       <c r="B490" s="2"/>
       <c r="C490" s="2"/>
@@ -31986,7 +31986,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="491" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A491" s="2" t="s">
         <v>29</v>
       </c>
@@ -32075,7 +32075,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="492" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A492" s="2"/>
       <c r="B492" s="2"/>
       <c r="C492" s="2"/>
@@ -32120,7 +32120,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="493" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A493" s="2"/>
       <c r="B493" s="2"/>
       <c r="C493" s="2"/>
@@ -32165,7 +32165,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="494" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A494" s="2" t="s">
         <v>29</v>
       </c>
@@ -32254,7 +32254,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="495" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A495" s="2"/>
       <c r="B495" s="2"/>
       <c r="C495" s="2"/>
@@ -32299,7 +32299,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="496" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A496" s="2" t="s">
         <v>29</v>
       </c>
@@ -32384,7 +32384,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="497" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A497" s="2"/>
       <c r="B497" s="2"/>
       <c r="C497" s="2"/>
@@ -32429,7 +32429,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="498" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A498" s="2"/>
       <c r="B498" s="2"/>
       <c r="C498" s="2"/>
@@ -32474,7 +32474,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="499" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A499" s="2"/>
       <c r="B499" s="2"/>
       <c r="C499" s="2"/>
@@ -32519,7 +32519,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="500" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A500" s="2"/>
       <c r="B500" s="2"/>
       <c r="C500" s="2"/>
@@ -32564,7 +32564,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="501" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A501" s="2" t="s">
         <v>29</v>
       </c>
@@ -32649,7 +32649,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="502" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A502" s="2"/>
       <c r="B502" s="2"/>
       <c r="C502" s="2"/>
@@ -32694,7 +32694,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="503" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A503" s="2"/>
       <c r="B503" s="2"/>
       <c r="C503" s="2"/>
@@ -32739,7 +32739,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="504" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A504" s="2"/>
       <c r="B504" s="2"/>
       <c r="C504" s="2"/>
@@ -32784,7 +32784,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="505" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A505" s="2"/>
       <c r="B505" s="2"/>
       <c r="C505" s="2"/>
@@ -32829,7 +32829,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="506" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A506" s="2" t="s">
         <v>29</v>
       </c>
@@ -32914,7 +32914,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="507" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A507" s="2"/>
       <c r="B507" s="2"/>
       <c r="C507" s="2"/>
@@ -32959,7 +32959,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="508" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A508" s="2"/>
       <c r="B508" s="2"/>
       <c r="C508" s="2"/>
@@ -33004,7 +33004,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="509" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A509" s="2"/>
       <c r="B509" s="2"/>
       <c r="C509" s="2"/>
@@ -33049,7 +33049,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="510" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A510" s="2"/>
       <c r="B510" s="2"/>
       <c r="C510" s="2"/>
@@ -33094,7 +33094,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="511" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A511" s="2"/>
       <c r="B511" s="2"/>
       <c r="C511" s="2"/>
@@ -33139,7 +33139,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="512" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A512" s="2" t="s">
         <v>29</v>
       </c>
@@ -33224,7 +33224,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="513" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A513" s="2"/>
       <c r="B513" s="2"/>
       <c r="C513" s="2"/>
@@ -33269,7 +33269,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="514" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A514" s="2"/>
       <c r="B514" s="2"/>
       <c r="C514" s="2"/>
@@ -33314,7 +33314,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="515" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A515" s="2"/>
       <c r="B515" s="2"/>
       <c r="C515" s="2"/>
@@ -33359,7 +33359,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="516" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A516" s="2"/>
       <c r="B516" s="2"/>
       <c r="C516" s="2"/>
@@ -33404,7 +33404,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="517" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A517" s="2"/>
       <c r="B517" s="2"/>
       <c r="C517" s="2"/>
@@ -33449,7 +33449,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="518" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A518" s="2" t="s">
         <v>29</v>
       </c>
@@ -33534,7 +33534,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="519" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A519" s="2"/>
       <c r="B519" s="2"/>
       <c r="C519" s="2"/>
@@ -33579,7 +33579,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="520" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A520" s="2"/>
       <c r="B520" s="2"/>
       <c r="C520" s="2"/>
@@ -33624,7 +33624,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="521" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A521" s="2"/>
       <c r="B521" s="2"/>
       <c r="C521" s="2"/>
@@ -33669,7 +33669,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="522" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A522" s="2" t="s">
         <v>29</v>
       </c>
@@ -33754,7 +33754,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="523" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A523" s="2"/>
       <c r="B523" s="2"/>
       <c r="C523" s="2"/>
@@ -33799,7 +33799,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="524" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A524" s="2"/>
       <c r="B524" s="2"/>
       <c r="C524" s="2"/>
@@ -33844,7 +33844,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="525" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A525" s="2"/>
       <c r="B525" s="2"/>
       <c r="C525" s="2"/>
@@ -33889,7 +33889,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="526" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A526" s="2"/>
       <c r="B526" s="2"/>
       <c r="C526" s="2"/>
@@ -33934,7 +33934,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="527" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A527" s="2" t="s">
         <v>29</v>
       </c>
@@ -34019,7 +34019,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="528" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A528" s="2"/>
       <c r="B528" s="2"/>
       <c r="C528" s="2"/>
@@ -34064,7 +34064,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="529" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A529" s="2"/>
       <c r="B529" s="2"/>
       <c r="C529" s="2"/>
@@ -34109,7 +34109,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="530" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A530" s="2" t="s">
         <v>29</v>
       </c>
@@ -34198,7 +34198,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="531" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A531" s="2"/>
       <c r="B531" s="2"/>
       <c r="C531" s="2"/>
@@ -34243,7 +34243,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="532" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A532" s="2"/>
       <c r="B532" s="2"/>
       <c r="C532" s="2"/>
@@ -34288,7 +34288,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="533" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A533" s="2"/>
       <c r="B533" s="2"/>
       <c r="C533" s="2"/>
@@ -34333,7 +34333,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="534" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A534" s="2" t="s">
         <v>29</v>
       </c>
@@ -34418,7 +34418,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="535" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A535" s="2"/>
       <c r="B535" s="2"/>
       <c r="C535" s="2"/>
@@ -34463,7 +34463,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="536" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A536" s="2"/>
       <c r="B536" s="2"/>
       <c r="C536" s="2"/>
@@ -34508,7 +34508,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="537" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A537" s="2"/>
       <c r="B537" s="2"/>
       <c r="C537" s="2"/>
@@ -34553,7 +34553,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="538" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A538" s="2"/>
       <c r="B538" s="2"/>
       <c r="C538" s="2"/>
@@ -34598,7 +34598,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="539" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A539" s="2"/>
       <c r="B539" s="2"/>
       <c r="C539" s="2"/>
@@ -34643,7 +34643,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="540" spans="1:29" ht="45" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A540" s="2" t="s">
         <v>29</v>
       </c>
@@ -34714,7 +34714,7 @@
       <c r="AB540" s="2"/>
       <c r="AC540" s="2"/>
     </row>
-    <row r="541" spans="1:29" ht="45" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A541" s="2" t="s">
         <v>29</v>
       </c>
@@ -34785,7 +34785,7 @@
       <c r="AB541" s="2"/>
       <c r="AC541" s="2"/>
     </row>
-    <row r="542" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A542" s="2" t="s">
         <v>29</v>
       </c>
@@ -34874,7 +34874,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="543" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A543" s="2"/>
       <c r="B543" s="2"/>
       <c r="C543" s="2"/>
@@ -34919,7 +34919,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="544" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A544" s="2"/>
       <c r="B544" s="2"/>
       <c r="C544" s="2"/>
@@ -34964,7 +34964,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="545" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A545" s="2"/>
       <c r="B545" s="2"/>
       <c r="C545" s="2"/>
@@ -35009,7 +35009,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="546" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A546" s="2"/>
       <c r="B546" s="2"/>
       <c r="C546" s="2"/>
@@ -35054,7 +35054,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="547" spans="1:29" ht="45" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A547" s="2" t="s">
         <v>29</v>
       </c>
@@ -35139,7 +35139,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="548" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A548" s="2"/>
       <c r="B548" s="2"/>
       <c r="C548" s="2"/>
@@ -35184,7 +35184,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="549" spans="1:29" ht="45" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A549" s="2" t="s">
         <v>29</v>
       </c>
@@ -35269,7 +35269,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="550" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A550" s="2"/>
       <c r="B550" s="2"/>
       <c r="C550" s="2"/>
@@ -35314,7 +35314,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="551" spans="1:29" ht="45" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:29" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A551" s="2" t="s">
         <v>29</v>
       </c>
@@ -35399,7 +35399,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="552" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A552" s="2"/>
       <c r="B552" s="2"/>
       <c r="C552" s="2"/>
@@ -35444,7 +35444,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="553" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A553" s="2"/>
       <c r="B553" s="2"/>
       <c r="C553" s="2"/>
@@ -35489,7 +35489,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="554" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A554" s="2"/>
       <c r="B554" s="2"/>
       <c r="C554" s="2"/>
@@ -35534,7 +35534,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="555" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A555" s="2" t="s">
         <v>29</v>
       </c>
@@ -35597,7 +35597,7 @@
       <c r="AB555" s="2"/>
       <c r="AC555" s="2"/>
     </row>
-    <row r="556" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A556" s="2" t="s">
         <v>29</v>
       </c>
@@ -35682,7 +35682,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="557" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A557" s="2"/>
       <c r="B557" s="2"/>
       <c r="C557" s="2"/>
@@ -35727,7 +35727,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="558" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A558" s="2"/>
       <c r="B558" s="2"/>
       <c r="C558" s="2"/>
@@ -35772,7 +35772,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="559" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A559" s="2" t="s">
         <v>29</v>
       </c>
@@ -35861,7 +35861,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="560" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A560" s="2"/>
       <c r="B560" s="2"/>
       <c r="C560" s="2"/>
@@ -35910,7 +35910,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="561" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A561" s="2"/>
       <c r="B561" s="2"/>
       <c r="C561" s="2"/>
@@ -35959,7 +35959,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="562" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A562" s="2"/>
       <c r="B562" s="2"/>
       <c r="C562" s="2"/>
@@ -36008,7 +36008,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="563" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A563" s="2"/>
       <c r="B563" s="2"/>
       <c r="C563" s="2"/>
@@ -36057,7 +36057,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="564" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A564" s="2"/>
       <c r="B564" s="2"/>
       <c r="C564" s="2"/>
@@ -36106,7 +36106,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="565" spans="1:29" ht="45" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:29" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A565" s="2" t="s">
         <v>29</v>
       </c>
@@ -36191,7 +36191,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="566" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A566" s="2"/>
       <c r="B566" s="2"/>
       <c r="C566" s="2"/>
@@ -36236,7 +36236,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="567" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A567" s="2"/>
       <c r="B567" s="2"/>
       <c r="C567" s="2"/>
@@ -36281,7 +36281,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="568" spans="1:29" ht="45" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:29" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A568" s="2" t="s">
         <v>29</v>
       </c>
@@ -36366,7 +36366,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="569" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A569" s="2"/>
       <c r="B569" s="2"/>
       <c r="C569" s="2"/>
@@ -36411,7 +36411,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="570" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A570" s="2"/>
       <c r="B570" s="2"/>
       <c r="C570" s="2"/>
@@ -36456,7 +36456,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="571" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A571" s="2"/>
       <c r="B571" s="2"/>
       <c r="C571" s="2"/>
@@ -36501,7 +36501,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="572" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A572" s="2" t="s">
         <v>29</v>
       </c>
@@ -36590,7 +36590,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="573" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A573" s="2"/>
       <c r="B573" s="2"/>
       <c r="C573" s="2"/>
@@ -36627,7 +36627,7 @@
       <c r="AB573" s="2"/>
       <c r="AC573" s="2"/>
     </row>
-    <row r="574" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A574" s="2"/>
       <c r="B574" s="2"/>
       <c r="C574" s="2"/>
@@ -36672,7 +36672,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="575" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A575" s="2"/>
       <c r="B575" s="2"/>
       <c r="C575" s="2"/>
@@ -36717,7 +36717,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="576" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A576" s="2"/>
       <c r="B576" s="2"/>
       <c r="C576" s="2"/>
@@ -36762,7 +36762,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="577" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A577" s="2"/>
       <c r="B577" s="2"/>
       <c r="C577" s="2"/>
@@ -36807,7 +36807,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="578" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A578" s="2" t="s">
         <v>29</v>
       </c>
@@ -36870,7 +36870,7 @@
       <c r="AB578" s="2"/>
       <c r="AC578" s="2"/>
     </row>
-    <row r="579" spans="1:29" ht="45" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A579" s="2" t="s">
         <v>29</v>
       </c>
@@ -36959,7 +36959,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="580" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A580" s="2"/>
       <c r="B580" s="2"/>
       <c r="C580" s="2"/>
@@ -37004,7 +37004,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="581" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A581" s="2"/>
       <c r="B581" s="2"/>
       <c r="C581" s="2"/>
@@ -37053,7 +37053,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="582" spans="1:29" ht="45" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A582" s="2" t="s">
         <v>29</v>
       </c>
@@ -37142,7 +37142,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="583" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A583" s="2"/>
       <c r="B583" s="2"/>
       <c r="C583" s="2"/>
@@ -37187,7 +37187,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="584" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A584" s="2" t="s">
         <v>29</v>
       </c>
@@ -37272,7 +37272,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="585" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A585" s="2"/>
       <c r="B585" s="2"/>
       <c r="C585" s="2"/>
@@ -37317,7 +37317,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="586" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A586" s="2"/>
       <c r="B586" s="2"/>
       <c r="C586" s="2"/>
@@ -37362,7 +37362,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="587" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A587" s="2"/>
       <c r="B587" s="2"/>
       <c r="C587" s="2"/>
@@ -37407,7 +37407,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="588" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A588" s="2" t="s">
         <v>29</v>
       </c>
@@ -37492,7 +37492,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="589" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A589" s="2"/>
       <c r="B589" s="2"/>
       <c r="C589" s="2"/>
@@ -37537,7 +37537,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="590" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A590" s="2"/>
       <c r="B590" s="2"/>
       <c r="C590" s="2"/>
@@ -37582,7 +37582,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="591" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A591" s="2"/>
       <c r="B591" s="2"/>
       <c r="C591" s="2"/>
@@ -37627,7 +37627,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="592" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A592" s="2"/>
       <c r="B592" s="2"/>
       <c r="C592" s="2"/>
@@ -37672,7 +37672,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="593" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A593" s="2" t="s">
         <v>29</v>
       </c>
@@ -37757,7 +37757,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="594" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A594" s="2"/>
       <c r="B594" s="2"/>
       <c r="C594" s="2"/>
@@ -37802,7 +37802,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="595" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A595" s="2"/>
       <c r="B595" s="2"/>
       <c r="C595" s="2"/>
@@ -37847,7 +37847,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="596" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A596" s="2"/>
       <c r="B596" s="2"/>
       <c r="C596" s="2"/>
@@ -37892,7 +37892,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="597" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A597" s="2"/>
       <c r="B597" s="2"/>
       <c r="C597" s="2"/>
@@ -37937,7 +37937,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="598" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A598" s="2"/>
       <c r="B598" s="2"/>
       <c r="C598" s="2"/>
@@ -37982,7 +37982,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="599" spans="1:29" ht="45" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:29" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A599" s="2" t="s">
         <v>29</v>
       </c>
@@ -38067,7 +38067,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="600" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A600" s="2"/>
       <c r="B600" s="2"/>
       <c r="C600" s="2"/>
@@ -38112,7 +38112,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="601" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A601" s="2"/>
       <c r="B601" s="2"/>
       <c r="C601" s="2"/>
@@ -38157,7 +38157,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="602" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A602" s="2"/>
       <c r="B602" s="2"/>
       <c r="C602" s="2"/>
@@ -38202,7 +38202,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="603" spans="1:29" ht="45" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A603" s="2"/>
       <c r="B603" s="2"/>
       <c r="C603" s="2"/>
@@ -38247,7 +38247,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="604" spans="1:29" ht="45" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:29" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A604" s="2" t="s">
         <v>29</v>
       </c>
@@ -38310,7 +38310,7 @@
       <c r="AB604" s="2"/>
       <c r="AC604" s="2"/>
     </row>
-    <row r="605" spans="1:29" ht="45" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:29" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A605" s="2" t="s">
         <v>29</v>
       </c>
@@ -38373,7 +38373,7 @@
       <c r="AB605" s="2"/>
       <c r="AC605" s="2"/>
     </row>
-    <row r="606" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A606" s="2" t="s">
         <v>29</v>
       </c>
@@ -38436,7 +38436,7 @@
       <c r="AB606" s="2"/>
       <c r="AC606" s="2"/>
     </row>
-    <row r="607" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:29" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A607" s="2" t="s">
         <v>29</v>
       </c>
